--- a/profiles/ldac/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/ldac/profile-crate/ro-crate-metadata.xlsx
@@ -2562,12 +2562,18 @@
     <t>ro-crate-metadata.json</t>
   </si>
   <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Hypertext Markup Language</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>Markdown</t>
   </si>
   <si>
@@ -2575,12 +2581,6 @@
   </si>
   <si>
     <t>JSON Data Interchange Format</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
-  </si>
-  <si>
-    <t>Hypertext Markup Language</t>
   </si>
 </sst>
 </file>

--- a/profiles/ldac/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/ldac/profile-crate/ro-crate-metadata.xlsx
@@ -1929,7 +1929,7 @@
     <t>The RO-Crate Metadata Descriptor</t>
   </si>
   <si>
-    <t>["#Root_Data_Entity", "#propertyValue_RO-Crate_Metadata_Descriptor.id"]</t>
+    <t>"#propertyValue_RO-Crate_Metadata_Descriptor.id"</t>
   </si>
   <si>
     <t>This is the 'magic' entity that identifies the RO-Crate Metadata Descriptor, which is the root of the graph and the entry point for validation. It must have a @type of RO-Crate_Metadata_Descriptor and its @id must be 'ro-crate-metadata.json'.</t>
